--- a/Noir Wingman/Assets/Sheets/Demo Dialogue/Olivia Meadows/OliviaDialogue 0.1.xlsx
+++ b/Noir Wingman/Assets/Sheets/Demo Dialogue/Olivia Meadows/OliviaDialogue 0.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coles\OneDrive\Desktop\NoirWingman\Noir Wingman\Assets\Sheets\Olivia Meadows\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b685ca5cabcdd482/Desktop/NoirWingman/Noir Wingman/Assets/Sheets/Demo Dialogue/Olivia Meadows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EDECFC7-95E3-4C4E-A821-48A388CB1988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{6EDECFC7-95E3-4C4E-A821-48A388CB1988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9D9DB50-300C-4E09-A33C-28DFB484E57B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{B7F00FD3-8E02-462F-86DF-9F799A3EC4EB}"/>
   </bookViews>
@@ -206,9 +206,6 @@
     <t>Olivia Meadows|Detective Juels|Olivia Meadows|Detective Juels|Olivia Meadows|Detective Juels|Detective Juels</t>
   </si>
   <si>
-    <t>For someone who loves asking hard questions, you don't seem to enjoy being on the receiving end. Tell me more about why you ordered an egg cream.</t>
-  </si>
-  <si>
     <t>Length</t>
   </si>
   <si>
@@ -218,10 +215,13 @@
     <t>Alcohol</t>
   </si>
   <si>
-    <t>egt</t>
-  </si>
-  <si>
     <t>Olivia Meadows| Detective Juels|Olivia Meadows|Detective Juels|Detective Juels|Olivia Meadows|Detective Juels</t>
+  </si>
+  <si>
+    <t>Egt</t>
+  </si>
+  <si>
+    <t>For lovin' to ask hard questions, you don't seem to enjoy receiving them, what's with the egg cream?</t>
   </si>
 </sst>
 </file>
@@ -277,6 +277,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -679,10 +683,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" t="s">
         <v>56</v>
-      </c>
-      <c r="I2" t="s">
-        <v>57</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -723,10 +727,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -735,7 +739,7 @@
         <v>30</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -749,7 +753,7 @@
         <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>37</v>
@@ -758,7 +762,7 @@
         <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
         <v>59</v>
@@ -767,10 +771,10 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" t="s">
         <v>56</v>
-      </c>
-      <c r="I4" t="s">
-        <v>57</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -811,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" t="s">
         <v>56</v>
-      </c>
-      <c r="I5" t="s">
-        <v>57</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -855,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" t="s">
         <v>56</v>
-      </c>
-      <c r="I6" t="s">
-        <v>57</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -890,7 +894,7 @@
         <v>46</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
         <v>59</v>
@@ -899,10 +903,10 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" t="s">
         <v>56</v>
-      </c>
-      <c r="I7" t="s">
-        <v>57</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -934,7 +938,7 @@
         <v>52</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>59</v>
@@ -943,10 +947,10 @@
         <v>2</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="J8">
         <v>1</v>

--- a/Noir Wingman/Assets/Sheets/Demo Dialogue/Olivia Meadows/OliviaDialogue 0.1.xlsx
+++ b/Noir Wingman/Assets/Sheets/Demo Dialogue/Olivia Meadows/OliviaDialogue 0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b685ca5cabcdd482/Desktop/NoirWingman/Noir Wingman/Assets/Sheets/Demo Dialogue/Olivia Meadows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{6EDECFC7-95E3-4C4E-A821-48A388CB1988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9D9DB50-300C-4E09-A33C-28DFB484E57B}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{6EDECFC7-95E3-4C4E-A821-48A388CB1988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42521365-98F2-4B3C-9F3C-A05DB708D261}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{B7F00FD3-8E02-462F-86DF-9F799A3EC4EB}"/>
   </bookViews>
